--- a/dist/assets/studylog-excel-import-template.xlsx
+++ b/dist/assets/studylog-excel-import-template.xlsx
@@ -582,7 +582,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>学迹 Studylog · Excel 导入模板</x:v>
+        <x:v>微光 Lumi · Excel 导入模板</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
